--- a/modelo/Meus_Gastos_Modelo.xlsx
+++ b/modelo/Meus_Gastos_Modelo.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Resumo" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Lançamentos" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Gastos Fixos" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Cartões" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Listas" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Entradas Fixas" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Cartões" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Listas" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Lançamentos!$A$4:$F$1004</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="125">
   <si>
     <t xml:space="preserve">Como usar</t>
   </si>
@@ -83,6 +84,15 @@
   </si>
   <si>
     <t xml:space="preserve">Contas que se repetem todo mês: descrição, categoria, dia do vencimento, valor, Ativo? (Sim/Não) e forma de pagamento. Marque "Pago" na coluna do mês quando pagar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entradas Fixas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aba "Entradas fixas"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que você recebe todo mês: descrição, categoria, dia do recebimento, valor e Ativa? (Sim/Não). Entra sozinho em todos os meses.</t>
   </si>
   <si>
     <t xml:space="preserve">Cartões</t>
@@ -178,7 +188,7 @@
     <t xml:space="preserve">Transporte</t>
   </si>
   <si>
-    <t xml:space="preserve">Entradas</t>
+    <t xml:space="preserve">Entradas (lançadas + fixas)</t>
   </si>
   <si>
     <t xml:space="preserve">Moradia</t>
@@ -238,6 +248,9 @@
     <t xml:space="preserve">Mês</t>
   </si>
   <si>
+    <t xml:space="preserve">Entradas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dia a dia (fora do cartão)</t>
   </si>
   <si>
@@ -283,7 +296,7 @@
     <t xml:space="preserve">Dez</t>
   </si>
   <si>
-    <t xml:space="preserve">Os gastos fixos ativos entram em todos os meses do ano. Encerrou uma conta? Mude "Ativo?" para "Não".</t>
+    <t xml:space="preserve">Os gastos fixos e as entradas fixas ativos entram em todos os meses do ano. Encerrou uma conta? Mude "Ativo?" para "Não".</t>
   </si>
   <si>
     <t xml:space="preserve">App → formulário "Lançar". Uma linha por gasto, entrada ou valor guardado. Valores sempre positivos.</t>
@@ -301,13 +314,13 @@
     <t xml:space="preserve">Forma de pagamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Salário (exemplo)</t>
+    <t xml:space="preserve">Bico de fim de semana (exemplo)</t>
   </si>
   <si>
     <t xml:space="preserve">Entrada</t>
   </si>
   <si>
-    <t xml:space="preserve">Salário</t>
+    <t xml:space="preserve">Renda extra</t>
   </si>
   <si>
     <t xml:space="preserve">Mercado (exemplo)</t>
@@ -338,6 +351,21 @@
   </si>
   <si>
     <t xml:space="preserve">Pago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App → aba "Entradas fixas". O que você recebe todo mês, como o salário. Entra sozinho em cada mês.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dia do recebimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ativa?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salário (exemplo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salário</t>
   </si>
   <si>
     <t xml:space="preserve">App → aba "Cartões". Uma linha por fatura, com o valor total e o vencimento.</t>
@@ -392,9 +420,6 @@
   </si>
   <si>
     <t xml:space="preserve">Adiantamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renda extra</t>
   </si>
   <si>
     <t xml:space="preserve">Reserva de emergência</t>
@@ -1046,11 +1071,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94804329"/>
-        <c:axId val="77761790"/>
+        <c:axId val="6846582"/>
+        <c:axId val="45436881"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94804329"/>
+        <c:axId val="6846582"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1082,7 +1107,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77761790"/>
+        <c:crossAx val="45436881"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1090,7 +1115,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77761790"/>
+        <c:axId val="45436881"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1132,7 +1157,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94804329"/>
+        <c:crossAx val="6846582"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1379,7 +1404,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -1467,32 +1492,43 @@
       <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="C10" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1525,26 +1561,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F4" s="8" t="n">
         <f aca="false">DATE($B$4,MATCH($E$4,{"Jan","Fev","Mar","Abr","Mai","Jun","Jul","Ago","Set","Out","Nov","Dez"},0),1)</f>
@@ -1553,43 +1589,43 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" s="10"/>
       <c r="D6" s="9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">B8+B9+B10</f>
         <v>1345.9</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))</f>
         <v>245.9</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E8" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D8,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D8,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D8)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D8,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1602,14 +1638,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim")-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
         <v>1100</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E9" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D9,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D9,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D9)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D9,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1622,14 +1658,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">SUMIFS(Cartões!$C$5:$C$204,Cartões!$B$5:$B$204,"&gt;="&amp;$F$4,Cartões!$B$5:$B$204,"&lt;="&amp;EOMONTH($F$4,0))</f>
         <v>0</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E10" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D10,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D10,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D10)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D10,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1642,14 +1678,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B11" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))</f>
-        <v>3200</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3450</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E11" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D11,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D11,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D11)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D11,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1662,14 +1698,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Guardado",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-2*SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Guardado",Lançamentos!$E$5:$E$1004,"Retirada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))</f>
         <v>0</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E12" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D12,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D12,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D12)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D12,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1682,14 +1718,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">B11-B7-B12</f>
-        <v>1854.1</v>
+        <v>2104.1</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D13,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D13,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D13)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D13,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1702,14 +1738,14 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Guardado",Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-2*SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Guardado",Lançamentos!$E$5:$E$1004,"Retirada",Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))</f>
         <v>0</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E14" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D14,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D14,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D14)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D14,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1722,14 +1758,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B15" s="15" t="n">
         <f aca="false">SUMPRODUCT('Gastos Fixos'!$D$5:$D$54*('Gastos Fixos'!$E$5:$E$54="Sim")*(INDEX('Gastos Fixos'!$G$5:$R$54,0,MONTH($F$4))&lt;&gt;"Pago"))</f>
         <v>0</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E15" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D15,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D15,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D15)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D15,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1742,14 +1778,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B16" s="15" t="n">
         <f aca="false">SUMIFS(Cartões!$C$5:$C$204,Cartões!$D$5:$D$204,"Aberta",Cartões!$B$5:$B$204,"&gt;="&amp;$F$4,Cartões!$B$5:$B$204,"&lt;="&amp;EOMONTH($F$4,0))</f>
         <v>0</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E16" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D16,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D16,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D16)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D16,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1762,14 +1798,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B17" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
         <v>0</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E17" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D17,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D17,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D17)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D17,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1782,7 +1818,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E18" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D18,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D18,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D18)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D18,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1795,7 +1831,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D19,Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$D$5:$D$1004,D19,Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;$F$4,Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH($F$4,0))+SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D19)-SUMIFS('Gastos Fixos'!$D$5:$D$54,'Gastos Fixos'!$E$5:$E$54,"Sim",'Gastos Fixos'!$B$5:$B$54,D19,'Gastos Fixos'!$F$5:$F$54,"Cartão de crédito")</f>
@@ -1808,7 +1844,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E20" s="15" t="n">
         <f aca="false">B10</f>
@@ -1821,7 +1857,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">SUM(E8:E20)</f>
@@ -1830,42 +1866,42 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B25" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,1,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,1,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,1,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,1,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C25" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,1,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,1,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,1,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,1,1),0))</f>
@@ -1889,16 +1925,16 @@
       </c>
       <c r="H25" s="15" t="n">
         <f aca="false">B25-F25-G25</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B26" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,2,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,2,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,2,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,2,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C26" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,2,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,2,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,2,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,2,1),0))</f>
@@ -1922,16 +1958,16 @@
       </c>
       <c r="H26" s="15" t="n">
         <f aca="false">B26-F26-G26</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B27" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,3,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,3,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,3,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,3,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C27" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,3,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,3,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,3,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,3,1),0))</f>
@@ -1955,16 +1991,16 @@
       </c>
       <c r="H27" s="15" t="n">
         <f aca="false">B27-F27-G27</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B28" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,4,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,4,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,4,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,4,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C28" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,4,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,4,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,4,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,4,1),0))</f>
@@ -1988,16 +2024,16 @@
       </c>
       <c r="H28" s="15" t="n">
         <f aca="false">B28-F28-G28</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B29" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,5,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,5,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,5,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,5,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C29" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,5,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,5,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,5,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,5,1),0))</f>
@@ -2021,16 +2057,16 @@
       </c>
       <c r="H29" s="15" t="n">
         <f aca="false">B29-F29-G29</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B30" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,6,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,6,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,6,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,6,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,6,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,6,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,6,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,6,1),0))</f>
@@ -2054,16 +2090,16 @@
       </c>
       <c r="H30" s="15" t="n">
         <f aca="false">B30-F30-G30</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B31" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,7,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,7,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,7,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,7,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C31" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,7,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,7,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,7,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,7,1),0))</f>
@@ -2087,16 +2123,16 @@
       </c>
       <c r="H31" s="15" t="n">
         <f aca="false">B31-F31-G31</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B32" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,8,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,8,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,8,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,8,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C32" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,8,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,8,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,8,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,8,1),0))</f>
@@ -2120,16 +2156,16 @@
       </c>
       <c r="H32" s="15" t="n">
         <f aca="false">B32-F32-G32</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B33" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,9,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,9,1),0))</f>
-        <v>3200</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,9,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,9,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3450</v>
       </c>
       <c r="C33" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,9,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,9,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,9,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,9,1),0))</f>
@@ -2153,16 +2189,16 @@
       </c>
       <c r="H33" s="15" t="n">
         <f aca="false">B33-F33-G33</f>
-        <v>1854.1</v>
+        <v>2104.1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B34" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,10,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,10,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,10,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,10,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C34" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,10,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,10,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,10,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,10,1),0))</f>
@@ -2186,16 +2222,16 @@
       </c>
       <c r="H34" s="15" t="n">
         <f aca="false">B34-F34-G34</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B35" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,11,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,11,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,11,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,11,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,11,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,11,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,11,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,11,1),0))</f>
@@ -2219,16 +2255,16 @@
       </c>
       <c r="H35" s="15" t="n">
         <f aca="false">B35-F35-G35</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B36" s="15" t="n">
-        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,12,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,12,1),0))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Entrada",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,12,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,12,1),0))+SUMIFS('Entradas Fixas'!$D$5:$D$34,'Entradas Fixas'!$E$5:$E$34,"Sim")</f>
+        <v>3200</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,12,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,12,1),0))-SUMIFS(Lançamentos!$F$5:$F$1004,Lançamentos!$C$5:$C$1004,"Gasto",Lançamentos!$E$5:$E$1004,"Cartão de crédito",Lançamentos!$A$5:$A$1004,"&gt;="&amp;DATE($B$4,12,1),Lançamentos!$A$5:$A$1004,"&lt;="&amp;EOMONTH(DATE($B$4,12,1),0))</f>
@@ -2252,12 +2288,12 @@
       </c>
       <c r="H36" s="15" t="n">
         <f aca="false">B36-F36-G36</f>
-        <v>-1100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2301,45 +2337,45 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="n">
-        <v>3200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2347,16 +2383,16 @@
         <v>46271</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>245.9</v>
@@ -10403,71 +10439,71 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>10</v>
@@ -10476,7 +10512,7 @@
         <v>1100</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="22"/>
@@ -10488,7 +10524,7 @@
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
       <c r="O5" s="22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P5" s="22"/>
       <c r="Q5" s="22"/>
@@ -11522,6 +11558,289 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="22"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="22"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="22"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="22"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="22"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="22"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="22"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="22"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="22"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="22"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="22"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Escolha uma opção da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B5:B34" type="list">
+      <formula1>Listas!$B$17:$B$19</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Escolha uma opção da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E34" type="list">
+      <formula1>Listas!$F$5:$F$6</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D204"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -11533,26 +11852,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12780,7 +13099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -12793,159 +13112,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="23" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="23" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="23" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="23" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="23" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="23" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="23" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
